--- a/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
@@ -1,80 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/interno/output/lista alimentos/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_C2CE303C08B9EDAC8FFE1F1F0B0A53129275BC7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{200E2935-60EC-42B3-8027-A2AC47CAB2D8}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>n_alimentos</t>
-  </si>
-  <si>
-    <t>Bogotá</t>
-  </si>
-  <si>
-    <t>Cúcuta</t>
-  </si>
-  <si>
-    <t>Barranquilla</t>
-  </si>
-  <si>
-    <t>Cartagena</t>
-  </si>
-  <si>
-    <t>Medellín</t>
-  </si>
-  <si>
-    <t>Bucaramanga</t>
-  </si>
-  <si>
-    <t>Cali</t>
-  </si>
-  <si>
-    <t>Montería</t>
-  </si>
-  <si>
-    <t>Villavicencio</t>
-  </si>
-  <si>
-    <t>Pereira</t>
-  </si>
-  <si>
-    <t>Manizales</t>
-  </si>
-  <si>
-    <t>Ibagué</t>
-  </si>
-  <si>
-    <t>Pasto</t>
-  </si>
-  <si>
-    <t>Cartagena De Indias</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_alimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bogotá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cúcuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barranquilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medellín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucaramanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montería</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villavicencio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manizales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibagué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -110,15 +100,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -400,14 +381,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,120 +393,112 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>173</v>
+      <c r="B14" t="n">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
@@ -20,43 +20,43 @@
     <t xml:space="preserve">n_alimentos</t>
   </si>
   <si>
+    <t xml:space="preserve">Barranquilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bogotá</t>
   </si>
   <si>
+    <t xml:space="preserve">Bucaramanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cali</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
     <t xml:space="preserve">Cúcuta</t>
   </si>
   <si>
-    <t xml:space="preserve">Barranquilla</t>
+    <t xml:space="preserve">Ibagué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manizales</t>
   </si>
   <si>
     <t xml:space="preserve">Medellín</t>
   </si>
   <si>
-    <t xml:space="preserve">Bucaramanga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cali</t>
-  </si>
-  <si>
     <t xml:space="preserve">Montería</t>
   </si>
   <si>
+    <t xml:space="preserve">Pasto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pereira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Villavicencio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manizales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ibagué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasto</t>
   </si>
 </sst>
 </file>
@@ -398,7 +398,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -406,7 +406,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -422,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -430,7 +430,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>175</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -446,7 +446,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -454,7 +454,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -462,7 +462,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -470,7 +470,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -478,7 +478,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>168</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -486,7 +486,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -494,7 +494,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>163</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
@@ -20,43 +20,43 @@
     <t xml:space="preserve">n_alimentos</t>
   </si>
   <si>
+    <t xml:space="preserve">Bogotá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucaramanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cali</t>
+  </si>
+  <si>
     <t xml:space="preserve">Barranquilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Bogotá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucaramanga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cali</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
+    <t xml:space="preserve">Montería</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pereira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cúcuta</t>
   </si>
   <si>
+    <t xml:space="preserve">Villavicencio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manizales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ibagué</t>
   </si>
   <si>
-    <t xml:space="preserve">Manizales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medellín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montería</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villavicencio</t>
   </si>
 </sst>
 </file>
@@ -398,7 +398,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
@@ -406,7 +406,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5">
@@ -422,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -430,7 +430,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -446,7 +446,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -454,7 +454,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -462,7 +462,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -470,7 +470,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -478,7 +478,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -486,7 +486,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -494,7 +494,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista alimentos/conteo_alimentos.xlsx
@@ -20,33 +20,36 @@
     <t xml:space="preserve">n_alimentos</t>
   </si>
   <si>
+    <t xml:space="preserve">Medellín</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bogotá</t>
   </si>
   <si>
     <t xml:space="preserve">Bucaramanga</t>
   </si>
   <si>
+    <t xml:space="preserve">Barranquilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cali</t>
   </si>
   <si>
-    <t xml:space="preserve">Barranquilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
+    <t xml:space="preserve">Pereira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montería</t>
   </si>
   <si>
-    <t xml:space="preserve">Pereira</t>
+    <t xml:space="preserve">Villavicencio</t>
   </si>
   <si>
     <t xml:space="preserve">Cúcuta</t>
   </si>
   <si>
-    <t xml:space="preserve">Villavicencio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pasto</t>
   </si>
   <si>
@@ -54,9 +57,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ibagué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medellín</t>
   </si>
 </sst>
 </file>
@@ -398,7 +398,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -406,7 +406,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -422,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
@@ -430,7 +430,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -438,7 +438,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
@@ -446,7 +446,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -454,7 +454,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -462,7 +462,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -470,7 +470,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -478,7 +478,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -486,7 +486,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -494,7 +494,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
